--- a/Game Components Assets/Jutland Torpedo ResolveV1.xlsx
+++ b/Game Components Assets/Jutland Torpedo ResolveV1.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12960"/>
+    <workbookView windowWidth="27945" windowHeight="12960" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="毁伤表" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="38">
   <si>
     <t>鱼雷型号</t>
   </si>
@@ -118,6 +118,9 @@
   </si>
   <si>
     <t>命中角度</t>
+  </si>
+  <si>
+    <t>罗经点数</t>
   </si>
   <si>
     <t>命中率</t>
@@ -183,45 +186,45 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0070C0"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFC00000"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="Times New Roman"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FFC00000"/>
-      <name val="黑体"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
@@ -421,7 +424,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="44">
+  <fills count="43">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -449,12 +452,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="0" tint="-0.15"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -958,7 +955,7 @@
     <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="14" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -982,16 +979,16 @@
     <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="14" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="15" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="15" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="16" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="28" fillId="13" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="14" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="14" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="15" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
@@ -1000,89 +997,89 @@
     <xf numFmtId="0" fontId="33" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="34" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="38" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="38" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="43" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="37" fillId="42" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="95">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1101,70 +1098,61 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1182,25 +1170,25 @@
     <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1209,13 +1197,13 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1224,55 +1212,52 @@
     <xf numFmtId="0" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="4" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1281,31 +1266,25 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
@@ -1314,62 +1293,77 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="19" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="10" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="19" fillId="10" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="19" fillId="10" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="6" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1696,829 +1690,832 @@
   <dimension ref="A1:S53"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="26" style="26" customWidth="1"/>
-    <col min="2" max="17" width="3.33333333333333" style="26" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="26"/>
+    <col min="1" max="1" width="26" style="23" customWidth="1"/>
+    <col min="2" max="17" width="3.33333333333333" style="23" customWidth="1"/>
+    <col min="18" max="18" width="9" style="23"/>
+    <col min="19" max="19" width="15.625" style="23" customWidth="1"/>
+    <col min="20" max="20" width="8.625" style="23" customWidth="1"/>
+    <col min="21" max="16384" width="9" style="23"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:19">
-      <c r="A1" s="27" t="s">
+      <c r="A1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
+      <c r="B1" s="25" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="29"/>
-      <c r="D1" s="29"/>
-      <c r="E1" s="30"/>
-      <c r="F1" s="31" t="s">
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="27"/>
+      <c r="F1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="G1" s="32"/>
-      <c r="H1" s="32"/>
-      <c r="I1" s="32"/>
-      <c r="J1" s="32"/>
-      <c r="K1" s="83"/>
-      <c r="L1" s="84" t="s">
+      <c r="G1" s="29"/>
+      <c r="H1" s="29"/>
+      <c r="I1" s="29"/>
+      <c r="J1" s="29"/>
+      <c r="K1" s="81"/>
+      <c r="L1" s="29" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="32"/>
-      <c r="N1" s="32"/>
-      <c r="O1" s="32"/>
-      <c r="P1" s="32"/>
-      <c r="Q1" s="83"/>
-      <c r="R1" s="94"/>
-      <c r="S1" s="95"/>
+      <c r="M1" s="29"/>
+      <c r="N1" s="29"/>
+      <c r="O1" s="29"/>
+      <c r="P1" s="29"/>
+      <c r="Q1" s="81"/>
+      <c r="R1" s="88"/>
+      <c r="S1" s="89"/>
     </row>
     <row r="2" customHeight="1" spans="1:19">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34">
+      <c r="A2" s="30"/>
+      <c r="B2" s="31">
         <v>1</v>
       </c>
-      <c r="C2" s="35">
+      <c r="C2" s="32">
         <v>2</v>
       </c>
-      <c r="D2" s="35">
+      <c r="D2" s="32">
         <v>3</v>
       </c>
-      <c r="E2" s="36">
+      <c r="E2" s="33">
         <v>4</v>
       </c>
-      <c r="F2" s="37">
+      <c r="F2" s="34">
         <v>5</v>
       </c>
-      <c r="G2" s="38">
+      <c r="G2" s="35">
         <v>6</v>
       </c>
-      <c r="H2" s="38">
+      <c r="H2" s="35">
         <v>7</v>
       </c>
-      <c r="I2" s="38">
+      <c r="I2" s="35">
         <v>8</v>
       </c>
-      <c r="J2" s="38">
+      <c r="J2" s="35">
         <v>9</v>
       </c>
-      <c r="K2" s="85">
+      <c r="K2" s="82">
         <v>10</v>
       </c>
-      <c r="L2" s="86">
+      <c r="L2" s="35">
         <v>5</v>
       </c>
-      <c r="M2" s="38">
+      <c r="M2" s="35">
         <v>6</v>
       </c>
-      <c r="N2" s="38">
+      <c r="N2" s="35">
         <v>7</v>
       </c>
-      <c r="O2" s="38">
+      <c r="O2" s="35">
         <v>8</v>
       </c>
-      <c r="P2" s="38">
+      <c r="P2" s="35">
         <v>9</v>
       </c>
-      <c r="Q2" s="85">
+      <c r="Q2" s="82">
         <v>10</v>
       </c>
-      <c r="R2" s="94"/>
-      <c r="S2" s="95"/>
+      <c r="R2" s="88"/>
+      <c r="S2" s="89"/>
     </row>
     <row r="3" customHeight="1" spans="1:19">
-      <c r="A3" s="39" t="s">
+      <c r="A3" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="41">
+      <c r="C3" s="38">
         <v>20</v>
       </c>
-      <c r="D3" s="42">
+      <c r="D3" s="39">
         <v>30</v>
       </c>
-      <c r="E3" s="43">
+      <c r="E3" s="40">
         <v>25</v>
       </c>
-      <c r="F3" s="40">
+      <c r="F3" s="37">
         <v>10</v>
       </c>
-      <c r="G3" s="43">
+      <c r="G3" s="40">
         <v>15</v>
       </c>
-      <c r="H3" s="42">
+      <c r="H3" s="39">
         <v>25</v>
       </c>
-      <c r="I3" s="42">
+      <c r="I3" s="39">
         <v>30</v>
       </c>
-      <c r="J3" s="87">
+      <c r="J3" s="83">
         <v>20</v>
       </c>
-      <c r="K3" s="87">
+      <c r="K3" s="83">
         <v>30</v>
       </c>
-      <c r="L3" s="40">
+      <c r="L3" s="37">
         <v>5</v>
       </c>
-      <c r="M3" s="41">
+      <c r="M3" s="38">
         <v>10</v>
       </c>
-      <c r="N3" s="43">
+      <c r="N3" s="40">
         <v>10</v>
       </c>
-      <c r="O3" s="42">
+      <c r="O3" s="39">
         <v>15</v>
       </c>
-      <c r="P3" s="42">
+      <c r="P3" s="39">
         <v>20</v>
       </c>
-      <c r="Q3" s="91">
+      <c r="Q3" s="86">
         <v>20</v>
       </c>
-      <c r="R3" s="94"/>
-      <c r="S3" s="95"/>
+      <c r="R3" s="88"/>
+      <c r="S3" s="89"/>
     </row>
     <row r="4" customHeight="1" spans="1:19">
-      <c r="A4" s="44" t="s">
+      <c r="A4" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="B4" s="45" t="s">
+      <c r="B4" s="42" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="46">
+      <c r="C4" s="43">
         <v>40</v>
       </c>
-      <c r="D4" s="47">
+      <c r="D4" s="44">
         <v>50</v>
       </c>
-      <c r="E4" s="48">
+      <c r="E4" s="45">
         <v>45</v>
       </c>
-      <c r="F4" s="49">
+      <c r="F4" s="46">
         <v>20</v>
       </c>
-      <c r="G4" s="50">
+      <c r="G4" s="47">
         <v>30</v>
       </c>
-      <c r="H4" s="51">
+      <c r="H4" s="48">
         <v>45</v>
       </c>
-      <c r="I4" s="51">
+      <c r="I4" s="48">
         <v>50</v>
       </c>
-      <c r="J4" s="88">
+      <c r="J4" s="84">
         <v>40</v>
       </c>
-      <c r="K4" s="88">
+      <c r="K4" s="84">
         <v>50</v>
       </c>
-      <c r="L4" s="49">
+      <c r="L4" s="46">
         <v>10</v>
       </c>
-      <c r="M4" s="62">
+      <c r="M4" s="58">
         <v>20</v>
       </c>
-      <c r="N4" s="50">
+      <c r="N4" s="47">
         <v>20</v>
       </c>
-      <c r="O4" s="51">
+      <c r="O4" s="48">
         <v>30</v>
       </c>
-      <c r="P4" s="51">
+      <c r="P4" s="48">
         <v>40</v>
       </c>
-      <c r="Q4" s="92">
+      <c r="Q4" s="87">
         <v>40</v>
       </c>
-      <c r="R4" s="94"/>
-      <c r="S4" s="95"/>
+      <c r="R4" s="88"/>
+      <c r="S4" s="89"/>
     </row>
     <row r="5" customHeight="1" spans="1:19">
-      <c r="A5" s="52"/>
-      <c r="B5" s="53">
+      <c r="A5" s="49"/>
+      <c r="B5" s="50">
         <v>1</v>
       </c>
-      <c r="C5" s="54">
+      <c r="C5" s="51">
         <v>2</v>
       </c>
-      <c r="D5" s="54">
+      <c r="D5" s="51">
         <v>3</v>
       </c>
-      <c r="E5" s="55">
+      <c r="E5" s="52">
         <v>4</v>
       </c>
-      <c r="F5" s="56">
+      <c r="F5" s="53">
         <v>5</v>
       </c>
-      <c r="G5" s="57">
+      <c r="G5" s="54">
         <v>6</v>
       </c>
-      <c r="H5" s="57">
+      <c r="H5" s="54">
         <v>7</v>
       </c>
-      <c r="I5" s="57">
+      <c r="I5" s="54">
         <v>8</v>
       </c>
-      <c r="J5" s="57">
+      <c r="J5" s="54">
         <v>9</v>
       </c>
-      <c r="K5" s="89">
+      <c r="K5" s="85">
         <v>10</v>
       </c>
-      <c r="L5" s="90">
+      <c r="L5" s="54">
         <v>5</v>
       </c>
-      <c r="M5" s="57">
+      <c r="M5" s="54">
         <v>6</v>
       </c>
-      <c r="N5" s="57">
+      <c r="N5" s="54">
         <v>7</v>
       </c>
-      <c r="O5" s="57">
+      <c r="O5" s="54">
         <v>8</v>
       </c>
-      <c r="P5" s="57">
+      <c r="P5" s="54">
         <v>9</v>
       </c>
-      <c r="Q5" s="89">
+      <c r="Q5" s="85">
         <v>10</v>
       </c>
-      <c r="R5" s="94"/>
-      <c r="S5" s="95"/>
+      <c r="R5" s="88"/>
+      <c r="S5" s="89"/>
     </row>
     <row r="6" customHeight="1" spans="1:19">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="55" t="s">
         <v>7</v>
       </c>
-      <c r="B6" s="40" t="s">
+      <c r="B6" s="37" t="s">
         <v>5</v>
       </c>
-      <c r="C6" s="41">
+      <c r="C6" s="38">
         <v>15</v>
       </c>
-      <c r="D6" s="42">
+      <c r="D6" s="39">
         <v>25</v>
       </c>
-      <c r="E6" s="59">
+      <c r="E6" s="56">
         <v>20</v>
       </c>
-      <c r="F6" s="40">
+      <c r="F6" s="37">
         <v>10</v>
       </c>
-      <c r="G6" s="43">
+      <c r="G6" s="40">
         <v>10</v>
       </c>
-      <c r="H6" s="42">
+      <c r="H6" s="39">
         <v>20</v>
       </c>
-      <c r="I6" s="42">
+      <c r="I6" s="39">
         <v>25</v>
       </c>
-      <c r="J6" s="87">
+      <c r="J6" s="83">
         <v>15</v>
       </c>
-      <c r="K6" s="91">
+      <c r="K6" s="86">
         <v>25</v>
       </c>
-      <c r="L6" s="40">
+      <c r="L6" s="37">
         <v>5</v>
       </c>
-      <c r="M6" s="43">
+      <c r="M6" s="40">
         <v>10</v>
       </c>
-      <c r="N6" s="42">
+      <c r="N6" s="39">
         <v>10</v>
       </c>
-      <c r="O6" s="42">
+      <c r="O6" s="39">
         <v>15</v>
       </c>
-      <c r="P6" s="42">
+      <c r="P6" s="39">
         <v>20</v>
       </c>
-      <c r="Q6" s="91">
+      <c r="Q6" s="86">
         <v>20</v>
       </c>
-      <c r="R6" s="94"/>
-      <c r="S6" s="95"/>
+      <c r="R6" s="88"/>
+      <c r="S6" s="89"/>
     </row>
     <row r="7" customHeight="1" spans="1:19">
-      <c r="A7" s="60" t="s">
+      <c r="A7" s="57" t="s">
         <v>8</v>
       </c>
-      <c r="B7" s="61" t="s">
+      <c r="B7" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="62">
+      <c r="C7" s="58">
         <v>35</v>
       </c>
-      <c r="D7" s="51">
+      <c r="D7" s="48">
         <v>45</v>
       </c>
-      <c r="E7" s="63">
+      <c r="E7" s="59">
         <v>40</v>
       </c>
-      <c r="F7" s="49">
+      <c r="F7" s="46">
         <v>15</v>
       </c>
-      <c r="G7" s="50">
+      <c r="G7" s="47">
         <v>25</v>
       </c>
-      <c r="H7" s="51">
+      <c r="H7" s="48">
         <v>40</v>
       </c>
-      <c r="I7" s="51">
+      <c r="I7" s="48">
         <v>45</v>
       </c>
-      <c r="J7" s="88">
+      <c r="J7" s="84">
         <v>35</v>
       </c>
-      <c r="K7" s="92">
+      <c r="K7" s="87">
         <v>45</v>
       </c>
-      <c r="L7" s="49">
+      <c r="L7" s="46">
         <v>10</v>
       </c>
-      <c r="M7" s="50">
+      <c r="M7" s="47">
         <v>15</v>
       </c>
-      <c r="N7" s="51">
+      <c r="N7" s="48">
         <v>25</v>
       </c>
-      <c r="O7" s="51">
+      <c r="O7" s="48">
         <v>35</v>
       </c>
-      <c r="P7" s="51">
+      <c r="P7" s="48">
         <v>40</v>
       </c>
-      <c r="Q7" s="92">
+      <c r="Q7" s="87">
         <v>40</v>
       </c>
-      <c r="R7" s="94"/>
-      <c r="S7" s="95"/>
+      <c r="R7" s="88"/>
+      <c r="S7" s="89"/>
     </row>
     <row r="8" customHeight="1" spans="1:19">
-      <c r="A8" s="64"/>
-      <c r="B8" s="65"/>
-      <c r="C8" s="65"/>
-      <c r="D8" s="65"/>
-      <c r="E8" s="65"/>
-      <c r="F8" s="65"/>
-      <c r="G8" s="65"/>
-      <c r="H8" s="65"/>
-      <c r="I8" s="65"/>
-      <c r="J8" s="65"/>
-      <c r="K8" s="65"/>
-      <c r="L8" s="93"/>
-      <c r="M8" s="93"/>
-      <c r="N8" s="93"/>
-      <c r="O8" s="93"/>
-      <c r="P8" s="93"/>
-      <c r="Q8" s="93"/>
-      <c r="R8" s="94"/>
-      <c r="S8" s="95"/>
+      <c r="A8" s="60"/>
+      <c r="B8" s="61"/>
+      <c r="C8" s="61"/>
+      <c r="D8" s="61"/>
+      <c r="E8" s="61"/>
+      <c r="F8" s="61"/>
+      <c r="G8" s="61"/>
+      <c r="H8" s="61"/>
+      <c r="I8" s="61"/>
+      <c r="J8" s="61"/>
+      <c r="K8" s="61"/>
+      <c r="L8" s="69"/>
+      <c r="M8" s="69"/>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+      <c r="Q8" s="69"/>
+      <c r="R8" s="88"/>
+      <c r="S8" s="89"/>
     </row>
     <row r="9" customHeight="1" spans="1:19">
-      <c r="A9" s="64"/>
-      <c r="B9" s="66"/>
-      <c r="C9" s="67" t="s">
+      <c r="A9" s="60"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="63" t="s">
         <v>9</v>
       </c>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
-      <c r="F9" s="67"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-      <c r="O9" s="68"/>
-      <c r="P9" s="68"/>
-      <c r="Q9" s="68"/>
-      <c r="R9" s="95"/>
-      <c r="S9" s="95"/>
+      <c r="D9" s="63"/>
+      <c r="E9" s="63"/>
+      <c r="F9" s="63"/>
+      <c r="G9" s="63"/>
+      <c r="H9" s="63"/>
+      <c r="I9" s="63"/>
+      <c r="J9" s="63"/>
+      <c r="K9" s="63"/>
+      <c r="L9" s="63"/>
+      <c r="M9" s="63"/>
+      <c r="N9" s="63"/>
+      <c r="O9" s="63"/>
+      <c r="P9" s="63"/>
+      <c r="Q9" s="90"/>
+      <c r="R9" s="89"/>
+      <c r="S9" s="89"/>
     </row>
     <row r="10" customHeight="1" spans="1:17">
-      <c r="A10" s="64"/>
-      <c r="B10" s="69"/>
-      <c r="C10" s="67" t="s">
+      <c r="A10" s="60"/>
+      <c r="B10" s="64"/>
+      <c r="C10" s="63" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="67"/>
-      <c r="E10" s="67"/>
-      <c r="F10" s="67"/>
-      <c r="G10" s="70" t="s">
+      <c r="D10" s="63"/>
+      <c r="E10" s="63"/>
+      <c r="F10" s="63"/>
+      <c r="G10" s="63" t="s">
         <v>11</v>
       </c>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-      <c r="O10" s="68"/>
-      <c r="P10" s="68"/>
-      <c r="Q10" s="68"/>
+      <c r="H10" s="63"/>
+      <c r="I10" s="63"/>
+      <c r="J10" s="63"/>
+      <c r="K10" s="63"/>
+      <c r="L10" s="63"/>
+      <c r="M10" s="63"/>
+      <c r="N10" s="63"/>
+      <c r="O10" s="63"/>
+      <c r="P10" s="63"/>
+      <c r="Q10" s="90"/>
     </row>
     <row r="11" customHeight="1" spans="1:17">
-      <c r="A11" s="71"/>
-      <c r="B11" s="72"/>
-      <c r="C11" s="73" t="s">
+      <c r="A11" s="65"/>
+      <c r="B11" s="66"/>
+      <c r="C11" s="67" t="s">
         <v>12</v>
       </c>
-      <c r="D11" s="74"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="68" t="s">
+      <c r="D11" s="68"/>
+      <c r="E11" s="68"/>
+      <c r="F11" s="68"/>
+      <c r="G11" s="63" t="s">
         <v>13</v>
       </c>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-      <c r="O11" s="68"/>
-      <c r="P11" s="68"/>
-      <c r="Q11" s="68"/>
+      <c r="H11" s="63"/>
+      <c r="I11" s="63"/>
+      <c r="J11" s="63"/>
+      <c r="K11" s="63"/>
+      <c r="L11" s="63"/>
+      <c r="M11" s="63"/>
+      <c r="N11" s="63"/>
+      <c r="O11" s="63"/>
+      <c r="P11" s="63"/>
+      <c r="Q11" s="90"/>
     </row>
     <row r="12" customHeight="1" spans="1:17">
-      <c r="A12" s="71"/>
-      <c r="B12" s="65"/>
-      <c r="C12" s="75"/>
-      <c r="D12" s="75"/>
-      <c r="E12" s="76"/>
-      <c r="F12" s="76"/>
-      <c r="G12" s="76"/>
-      <c r="H12" s="76"/>
-      <c r="I12" s="76"/>
-      <c r="J12" s="76"/>
-      <c r="K12" s="76"/>
-      <c r="L12" s="65"/>
-      <c r="M12" s="81"/>
-      <c r="N12" s="81"/>
-      <c r="O12" s="81"/>
-      <c r="P12" s="81"/>
-      <c r="Q12" s="81"/>
+      <c r="A12" s="65"/>
+      <c r="B12" s="61"/>
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="70"/>
+      <c r="F12" s="70"/>
+      <c r="G12" s="70"/>
+      <c r="H12" s="70"/>
+      <c r="I12" s="70"/>
+      <c r="J12" s="70"/>
+      <c r="K12" s="70"/>
+      <c r="L12" s="61"/>
+      <c r="M12" s="70"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="70"/>
+      <c r="P12" s="70"/>
+      <c r="Q12" s="70"/>
     </row>
     <row r="13" customHeight="1" spans="1:17">
-      <c r="A13" s="71"/>
-      <c r="B13" s="77" t="s">
+      <c r="A13" s="65"/>
+      <c r="B13" s="71" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="77"/>
-      <c r="D13" s="77"/>
-      <c r="E13" s="78" t="s">
+      <c r="C13" s="72"/>
+      <c r="D13" s="72"/>
+      <c r="E13" s="73" t="s">
         <v>9</v>
       </c>
-      <c r="F13" s="78"/>
-      <c r="G13" s="78"/>
-      <c r="H13" s="78"/>
-      <c r="I13" s="78"/>
-      <c r="J13" s="78"/>
-      <c r="K13" s="78"/>
-      <c r="L13" s="78"/>
-      <c r="M13" s="78"/>
-      <c r="N13" s="78"/>
-      <c r="O13" s="78"/>
-      <c r="P13" s="78"/>
-      <c r="Q13" s="78"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
+      <c r="J13" s="73"/>
+      <c r="K13" s="73"/>
+      <c r="L13" s="73"/>
+      <c r="M13" s="73"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="73"/>
+      <c r="P13" s="73"/>
+      <c r="Q13" s="91"/>
     </row>
     <row r="14" customHeight="1" spans="1:17">
-      <c r="A14" s="64"/>
-      <c r="B14" s="79" t="s">
+      <c r="A14" s="60"/>
+      <c r="B14" s="74" t="s">
         <v>15</v>
       </c>
-      <c r="C14" s="79"/>
-      <c r="D14" s="79"/>
-      <c r="E14" s="80" t="s">
+      <c r="C14" s="75"/>
+      <c r="D14" s="75"/>
+      <c r="E14" s="76" t="s">
         <v>16</v>
       </c>
-      <c r="F14" s="80"/>
-      <c r="G14" s="80"/>
-      <c r="H14" s="80"/>
-      <c r="I14" s="80"/>
-      <c r="J14" s="80"/>
-      <c r="K14" s="80"/>
-      <c r="L14" s="80"/>
-      <c r="M14" s="80"/>
-      <c r="N14" s="80"/>
-      <c r="O14" s="80"/>
-      <c r="P14" s="80"/>
-      <c r="Q14" s="80"/>
+      <c r="F14" s="76"/>
+      <c r="G14" s="76"/>
+      <c r="H14" s="76"/>
+      <c r="I14" s="76"/>
+      <c r="J14" s="76"/>
+      <c r="K14" s="76"/>
+      <c r="L14" s="76"/>
+      <c r="M14" s="76"/>
+      <c r="N14" s="76"/>
+      <c r="O14" s="76"/>
+      <c r="P14" s="76"/>
+      <c r="Q14" s="92"/>
     </row>
     <row r="15" customHeight="1" spans="1:17">
-      <c r="A15" s="64"/>
-      <c r="B15" s="79" t="s">
+      <c r="A15" s="60"/>
+      <c r="B15" s="74" t="s">
         <v>17</v>
       </c>
-      <c r="C15" s="79"/>
-      <c r="D15" s="79"/>
-      <c r="E15" s="80" t="s">
+      <c r="C15" s="75"/>
+      <c r="D15" s="75"/>
+      <c r="E15" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="F15" s="80"/>
-      <c r="G15" s="80"/>
-      <c r="H15" s="80"/>
-      <c r="I15" s="80"/>
-      <c r="J15" s="80"/>
-      <c r="K15" s="80"/>
-      <c r="L15" s="80"/>
-      <c r="M15" s="80"/>
-      <c r="N15" s="80"/>
-      <c r="O15" s="80"/>
-      <c r="P15" s="80"/>
-      <c r="Q15" s="80"/>
+      <c r="F15" s="76"/>
+      <c r="G15" s="76"/>
+      <c r="H15" s="76"/>
+      <c r="I15" s="76"/>
+      <c r="J15" s="76"/>
+      <c r="K15" s="76"/>
+      <c r="L15" s="76"/>
+      <c r="M15" s="76"/>
+      <c r="N15" s="76"/>
+      <c r="O15" s="76"/>
+      <c r="P15" s="76"/>
+      <c r="Q15" s="92"/>
     </row>
     <row r="16" customHeight="1" spans="1:17">
-      <c r="A16" s="81"/>
-      <c r="B16" s="79" t="s">
+      <c r="A16" s="70"/>
+      <c r="B16" s="74" t="s">
         <v>19</v>
       </c>
-      <c r="C16" s="79"/>
-      <c r="D16" s="79"/>
-      <c r="E16" s="80" t="s">
+      <c r="C16" s="75"/>
+      <c r="D16" s="75"/>
+      <c r="E16" s="76" t="s">
         <v>20</v>
       </c>
-      <c r="F16" s="80"/>
-      <c r="G16" s="80"/>
-      <c r="H16" s="80"/>
-      <c r="I16" s="80"/>
-      <c r="J16" s="80"/>
-      <c r="K16" s="80"/>
-      <c r="L16" s="80"/>
-      <c r="M16" s="80"/>
-      <c r="N16" s="80"/>
-      <c r="O16" s="80"/>
-      <c r="P16" s="80"/>
-      <c r="Q16" s="80"/>
+      <c r="F16" s="76"/>
+      <c r="G16" s="76"/>
+      <c r="H16" s="76"/>
+      <c r="I16" s="76"/>
+      <c r="J16" s="76"/>
+      <c r="K16" s="76"/>
+      <c r="L16" s="76"/>
+      <c r="M16" s="76"/>
+      <c r="N16" s="76"/>
+      <c r="O16" s="76"/>
+      <c r="P16" s="76"/>
+      <c r="Q16" s="92"/>
     </row>
     <row r="17" customHeight="1" spans="1:17">
-      <c r="A17" s="81"/>
-      <c r="B17" s="79" t="s">
+      <c r="A17" s="70"/>
+      <c r="B17" s="74" t="s">
         <v>21</v>
       </c>
-      <c r="C17" s="79"/>
-      <c r="D17" s="79"/>
-      <c r="E17" s="82" t="s">
+      <c r="C17" s="75"/>
+      <c r="D17" s="75"/>
+      <c r="E17" s="77" t="s">
         <v>22</v>
       </c>
-      <c r="F17" s="82"/>
-      <c r="G17" s="82"/>
-      <c r="H17" s="82"/>
-      <c r="I17" s="82"/>
-      <c r="J17" s="82"/>
-      <c r="K17" s="82"/>
-      <c r="L17" s="82"/>
-      <c r="M17" s="82"/>
-      <c r="N17" s="82"/>
-      <c r="O17" s="82"/>
-      <c r="P17" s="82"/>
-      <c r="Q17" s="82"/>
+      <c r="F17" s="77"/>
+      <c r="G17" s="77"/>
+      <c r="H17" s="77"/>
+      <c r="I17" s="77"/>
+      <c r="J17" s="77"/>
+      <c r="K17" s="77"/>
+      <c r="L17" s="77"/>
+      <c r="M17" s="77"/>
+      <c r="N17" s="77"/>
+      <c r="O17" s="77"/>
+      <c r="P17" s="77"/>
+      <c r="Q17" s="93"/>
     </row>
     <row r="18" customHeight="1" spans="1:17">
-      <c r="A18" s="81"/>
-      <c r="B18" s="79" t="s">
+      <c r="A18" s="70"/>
+      <c r="B18" s="74" t="s">
         <v>23</v>
       </c>
-      <c r="C18" s="79"/>
-      <c r="D18" s="79"/>
-      <c r="E18" s="82" t="s">
+      <c r="C18" s="75"/>
+      <c r="D18" s="75"/>
+      <c r="E18" s="77" t="s">
         <v>24</v>
       </c>
-      <c r="F18" s="82"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="82"/>
-      <c r="P18" s="82"/>
-      <c r="Q18" s="82"/>
+      <c r="F18" s="77"/>
+      <c r="G18" s="77"/>
+      <c r="H18" s="77"/>
+      <c r="I18" s="77"/>
+      <c r="J18" s="77"/>
+      <c r="K18" s="77"/>
+      <c r="L18" s="77"/>
+      <c r="M18" s="77"/>
+      <c r="N18" s="77"/>
+      <c r="O18" s="77"/>
+      <c r="P18" s="77"/>
+      <c r="Q18" s="93"/>
     </row>
     <row r="19" customHeight="1" spans="1:17">
-      <c r="A19" s="81"/>
-      <c r="B19" s="79" t="s">
+      <c r="A19" s="70"/>
+      <c r="B19" s="74" t="s">
         <v>25</v>
       </c>
-      <c r="C19" s="79"/>
-      <c r="D19" s="79"/>
-      <c r="E19" s="82" t="s">
+      <c r="C19" s="75"/>
+      <c r="D19" s="75"/>
+      <c r="E19" s="77" t="s">
         <v>26</v>
       </c>
-      <c r="F19" s="82"/>
-      <c r="G19" s="82"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
-      <c r="O19" s="82"/>
-      <c r="P19" s="82"/>
-      <c r="Q19" s="82"/>
+      <c r="F19" s="77"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="77"/>
+      <c r="K19" s="77"/>
+      <c r="L19" s="77"/>
+      <c r="M19" s="77"/>
+      <c r="N19" s="77"/>
+      <c r="O19" s="77"/>
+      <c r="P19" s="77"/>
+      <c r="Q19" s="93"/>
     </row>
     <row r="20" customHeight="1" spans="1:17">
-      <c r="A20" s="81"/>
-      <c r="B20" s="79" t="s">
+      <c r="A20" s="70"/>
+      <c r="B20" s="78" t="s">
         <v>27</v>
       </c>
       <c r="C20" s="79"/>
       <c r="D20" s="79"/>
-      <c r="E20" s="82" t="s">
+      <c r="E20" s="80" t="s">
         <v>28</v>
       </c>
-      <c r="F20" s="82"/>
-      <c r="G20" s="82"/>
-      <c r="H20" s="82"/>
-      <c r="I20" s="82"/>
-      <c r="J20" s="82"/>
-      <c r="K20" s="82"/>
-      <c r="L20" s="82"/>
-      <c r="M20" s="82"/>
-      <c r="N20" s="82"/>
-      <c r="O20" s="82"/>
-      <c r="P20" s="82"/>
-      <c r="Q20" s="82"/>
+      <c r="F20" s="80"/>
+      <c r="G20" s="80"/>
+      <c r="H20" s="80"/>
+      <c r="I20" s="80"/>
+      <c r="J20" s="80"/>
+      <c r="K20" s="80"/>
+      <c r="L20" s="80"/>
+      <c r="M20" s="80"/>
+      <c r="N20" s="80"/>
+      <c r="O20" s="80"/>
+      <c r="P20" s="80"/>
+      <c r="Q20" s="94"/>
     </row>
     <row r="21" customHeight="1" spans="1:17">
-      <c r="A21" s="81"/>
-      <c r="B21" s="76"/>
-      <c r="C21" s="76"/>
-      <c r="D21" s="76"/>
-      <c r="E21" s="76"/>
-      <c r="F21" s="76"/>
-      <c r="G21" s="76"/>
-      <c r="H21" s="76"/>
-      <c r="I21" s="76"/>
-      <c r="J21" s="76"/>
-      <c r="K21" s="76"/>
-      <c r="L21" s="81"/>
-      <c r="M21" s="81"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="81"/>
-      <c r="P21" s="81"/>
-      <c r="Q21" s="81"/>
+      <c r="A21" s="70"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="70"/>
+      <c r="D21" s="70"/>
+      <c r="E21" s="70"/>
+      <c r="F21" s="70"/>
+      <c r="G21" s="70"/>
+      <c r="H21" s="70"/>
+      <c r="I21" s="70"/>
+      <c r="J21" s="70"/>
+      <c r="K21" s="70"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="70"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="70"/>
+      <c r="P21" s="70"/>
+      <c r="Q21" s="70"/>
     </row>
     <row r="22" customHeight="1" spans="1:17">
-      <c r="A22" s="81"/>
-      <c r="B22" s="76"/>
-      <c r="C22" s="76"/>
-      <c r="D22" s="76"/>
-      <c r="E22" s="76"/>
-      <c r="F22" s="76"/>
-      <c r="G22" s="76"/>
-      <c r="H22" s="76"/>
-      <c r="I22" s="76"/>
-      <c r="J22" s="76"/>
-      <c r="K22" s="76"/>
-      <c r="L22" s="81"/>
-      <c r="M22" s="81"/>
-      <c r="N22" s="81"/>
-      <c r="O22" s="81"/>
-      <c r="P22" s="81"/>
-      <c r="Q22" s="81"/>
+      <c r="A22" s="70"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="70"/>
+      <c r="D22" s="70"/>
+      <c r="E22" s="70"/>
+      <c r="F22" s="70"/>
+      <c r="G22" s="70"/>
+      <c r="H22" s="70"/>
+      <c r="I22" s="70"/>
+      <c r="J22" s="70"/>
+      <c r="K22" s="70"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="70"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="70"/>
+      <c r="P22" s="70"/>
+      <c r="Q22" s="70"/>
     </row>
     <row r="23" customHeight="1" spans="1:17">
-      <c r="A23" s="81"/>
-      <c r="B23" s="76"/>
-      <c r="C23" s="76"/>
-      <c r="D23" s="76"/>
-      <c r="E23" s="76"/>
-      <c r="F23" s="76"/>
-      <c r="G23" s="76"/>
-      <c r="H23" s="76"/>
-      <c r="I23" s="76"/>
-      <c r="J23" s="76"/>
-      <c r="K23" s="76"/>
-      <c r="L23" s="81"/>
-      <c r="M23" s="81"/>
-      <c r="N23" s="81"/>
-      <c r="O23" s="81"/>
-      <c r="P23" s="81"/>
-      <c r="Q23" s="81"/>
+      <c r="A23" s="70"/>
+      <c r="B23" s="70"/>
+      <c r="C23" s="70"/>
+      <c r="D23" s="70"/>
+      <c r="E23" s="70"/>
+      <c r="F23" s="70"/>
+      <c r="G23" s="70"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="70"/>
+      <c r="J23" s="70"/>
+      <c r="K23" s="70"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="70"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="70"/>
+      <c r="P23" s="70"/>
+      <c r="Q23" s="70"/>
     </row>
     <row r="24" customHeight="1" spans="1:17">
-      <c r="A24" s="81"/>
-      <c r="B24" s="76"/>
-      <c r="C24" s="76"/>
-      <c r="D24" s="76"/>
-      <c r="E24" s="76"/>
-      <c r="F24" s="76"/>
-      <c r="G24" s="76"/>
-      <c r="H24" s="76"/>
-      <c r="I24" s="76"/>
-      <c r="J24" s="76"/>
-      <c r="K24" s="76"/>
-      <c r="L24" s="81"/>
-      <c r="M24" s="81"/>
-      <c r="N24" s="81"/>
-      <c r="O24" s="81"/>
-      <c r="P24" s="81"/>
-      <c r="Q24" s="81"/>
+      <c r="A24" s="70"/>
+      <c r="B24" s="70"/>
+      <c r="C24" s="70"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="70"/>
+      <c r="K24" s="70"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="70"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="70"/>
+      <c r="P24" s="70"/>
+      <c r="Q24" s="70"/>
     </row>
     <row r="25" customHeight="1" spans="1:17">
-      <c r="A25" s="81"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="76"/>
-      <c r="D25" s="76"/>
-      <c r="E25" s="76"/>
-      <c r="F25" s="76"/>
-      <c r="G25" s="76"/>
-      <c r="H25" s="76"/>
-      <c r="I25" s="76"/>
-      <c r="J25" s="76"/>
-      <c r="K25" s="76"/>
-      <c r="L25" s="81"/>
-      <c r="M25" s="81"/>
-      <c r="N25" s="81"/>
-      <c r="O25" s="81"/>
-      <c r="P25" s="81"/>
-      <c r="Q25" s="81"/>
+      <c r="A25" s="70"/>
+      <c r="B25" s="70"/>
+      <c r="C25" s="70"/>
+      <c r="D25" s="70"/>
+      <c r="E25" s="70"/>
+      <c r="F25" s="70"/>
+      <c r="G25" s="70"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="70"/>
+      <c r="J25" s="70"/>
+      <c r="K25" s="70"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="70"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="70"/>
+      <c r="P25" s="70"/>
+      <c r="Q25" s="70"/>
     </row>
     <row r="26" customHeight="1" spans="1:17">
-      <c r="A26" s="81"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="76"/>
-      <c r="D26" s="76"/>
-      <c r="E26" s="76"/>
-      <c r="F26" s="76"/>
-      <c r="G26" s="76"/>
-      <c r="H26" s="76"/>
-      <c r="I26" s="76"/>
-      <c r="J26" s="76"/>
-      <c r="K26" s="76"/>
-      <c r="L26" s="81"/>
-      <c r="M26" s="81"/>
-      <c r="N26" s="81"/>
-      <c r="O26" s="81"/>
-      <c r="P26" s="81"/>
-      <c r="Q26" s="81"/>
+      <c r="A26" s="70"/>
+      <c r="B26" s="70"/>
+      <c r="C26" s="70"/>
+      <c r="D26" s="70"/>
+      <c r="E26" s="70"/>
+      <c r="F26" s="70"/>
+      <c r="G26" s="70"/>
+      <c r="H26" s="70"/>
+      <c r="I26" s="70"/>
+      <c r="J26" s="70"/>
+      <c r="K26" s="70"/>
+      <c r="L26" s="70"/>
+      <c r="M26" s="70"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="70"/>
+      <c r="P26" s="70"/>
+      <c r="Q26" s="70"/>
     </row>
     <row r="27" customHeight="1" spans="1:17">
-      <c r="A27" s="81"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="76"/>
-      <c r="D27" s="76"/>
-      <c r="E27" s="76"/>
-      <c r="F27" s="76"/>
-      <c r="G27" s="76"/>
-      <c r="H27" s="76"/>
-      <c r="I27" s="76"/>
-      <c r="J27" s="76"/>
-      <c r="K27" s="76"/>
-      <c r="L27" s="81"/>
-      <c r="M27" s="81"/>
-      <c r="N27" s="81"/>
-      <c r="O27" s="81"/>
-      <c r="P27" s="81"/>
-      <c r="Q27" s="81"/>
+      <c r="A27" s="70"/>
+      <c r="B27" s="70"/>
+      <c r="C27" s="70"/>
+      <c r="D27" s="70"/>
+      <c r="E27" s="70"/>
+      <c r="F27" s="70"/>
+      <c r="G27" s="70"/>
+      <c r="H27" s="70"/>
+      <c r="I27" s="70"/>
+      <c r="J27" s="70"/>
+      <c r="K27" s="70"/>
+      <c r="L27" s="70"/>
+      <c r="M27" s="70"/>
+      <c r="N27" s="70"/>
+      <c r="O27" s="70"/>
+      <c r="P27" s="70"/>
+      <c r="Q27" s="70"/>
     </row>
     <row r="28" customHeight="1" spans="1:17">
-      <c r="A28" s="81"/>
-      <c r="B28" s="76"/>
-      <c r="C28" s="76"/>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76"/>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="76"/>
-      <c r="K28" s="76"/>
-      <c r="L28" s="81"/>
-      <c r="M28" s="81"/>
-      <c r="N28" s="81"/>
-      <c r="O28" s="81"/>
-      <c r="P28" s="81"/>
-      <c r="Q28" s="81"/>
+      <c r="A28" s="70"/>
+      <c r="B28" s="70"/>
+      <c r="C28" s="70"/>
+      <c r="D28" s="70"/>
+      <c r="E28" s="70"/>
+      <c r="F28" s="70"/>
+      <c r="G28" s="70"/>
+      <c r="H28" s="70"/>
+      <c r="I28" s="70"/>
+      <c r="J28" s="70"/>
+      <c r="K28" s="70"/>
+      <c r="L28" s="70"/>
+      <c r="M28" s="70"/>
+      <c r="N28" s="70"/>
+      <c r="O28" s="70"/>
+      <c r="P28" s="70"/>
+      <c r="Q28" s="70"/>
     </row>
     <row r="29" customHeight="1" spans="1:17">
-      <c r="A29" s="81"/>
-      <c r="B29" s="76"/>
-      <c r="C29" s="76"/>
-      <c r="D29" s="76"/>
-      <c r="E29" s="76"/>
-      <c r="F29" s="76"/>
-      <c r="G29" s="76"/>
-      <c r="H29" s="76"/>
-      <c r="I29" s="76"/>
-      <c r="J29" s="76"/>
-      <c r="K29" s="76"/>
-      <c r="L29" s="81"/>
-      <c r="M29" s="81"/>
-      <c r="N29" s="81"/>
-      <c r="O29" s="81"/>
-      <c r="P29" s="81"/>
-      <c r="Q29" s="81"/>
+      <c r="A29" s="70"/>
+      <c r="B29" s="70"/>
+      <c r="C29" s="70"/>
+      <c r="D29" s="70"/>
+      <c r="E29" s="70"/>
+      <c r="F29" s="70"/>
+      <c r="G29" s="70"/>
+      <c r="H29" s="70"/>
+      <c r="I29" s="70"/>
+      <c r="J29" s="70"/>
+      <c r="K29" s="70"/>
+      <c r="L29" s="70"/>
+      <c r="M29" s="70"/>
+      <c r="N29" s="70"/>
+      <c r="O29" s="70"/>
+      <c r="P29" s="70"/>
+      <c r="Q29" s="70"/>
     </row>
     <row r="30" customHeight="1" spans="2:11">
       <c r="B30"/>
@@ -2849,199 +2846,232 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="15.625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="8.375" style="1" customWidth="1"/>
-    <col min="4" max="4" width="7.125" style="1" customWidth="1"/>
-    <col min="5" max="5" width="9.75" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="7.375" style="1" customWidth="1"/>
-    <col min="8" max="16384" width="9" style="1"/>
+    <col min="2" max="3" width="8.625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="8.375" style="1" customWidth="1"/>
+    <col min="5" max="5" width="7.125" style="1" customWidth="1"/>
+    <col min="6" max="6" width="9.75" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="7.375" style="1" customWidth="1"/>
+    <col min="9" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1" spans="1:8">
+    <row r="1" ht="20" customHeight="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="6"/>
-      <c r="H1" s="7"/>
-    </row>
-    <row r="2" ht="20" customHeight="1" spans="1:8">
-      <c r="A2" s="8"/>
-      <c r="B2" s="9"/>
-      <c r="C2" s="10"/>
-      <c r="D2" s="11"/>
-      <c r="E2" s="12"/>
-      <c r="H2" s="7"/>
-    </row>
-    <row r="3" ht="20" customHeight="1" spans="1:8">
-      <c r="A3" s="13" t="s">
+      <c r="C1" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B3" s="14">
+      <c r="D1" s="4"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="I1" s="22"/>
+    </row>
+    <row r="2" ht="20" customHeight="1" spans="1:9">
+      <c r="A2" s="6"/>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="5"/>
+      <c r="F2" s="5"/>
+      <c r="I2" s="22"/>
+    </row>
+    <row r="3" ht="20" customHeight="1" spans="1:9">
+      <c r="A3" s="8" t="s">
+        <v>32</v>
+      </c>
+      <c r="B3" s="9">
+        <v>3</v>
+      </c>
+      <c r="C3" s="10">
         <v>0.03</v>
       </c>
-      <c r="C3" s="15"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="H3" s="7"/>
-    </row>
-    <row r="4" ht="20" customHeight="1" spans="1:8">
-      <c r="A4" s="13" t="s">
-        <v>32</v>
-      </c>
-      <c r="B4" s="14">
+      <c r="D3" s="11"/>
+      <c r="E3" s="12"/>
+      <c r="F3" s="12"/>
+      <c r="I3" s="22"/>
+    </row>
+    <row r="4" ht="20" customHeight="1" spans="1:9">
+      <c r="A4" s="8" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" s="9">
+        <v>2</v>
+      </c>
+      <c r="C4" s="10">
         <v>0.08</v>
       </c>
-      <c r="C4" s="15"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="H4" s="7"/>
-    </row>
-    <row r="5" ht="20" customHeight="1" spans="1:8">
-      <c r="A5" s="13" t="s">
-        <v>33</v>
-      </c>
-      <c r="B5" s="14">
+      <c r="D4" s="11"/>
+      <c r="E4" s="12"/>
+      <c r="F4" s="12"/>
+      <c r="I4" s="22"/>
+    </row>
+    <row r="5" ht="20" customHeight="1" spans="1:9">
+      <c r="A5" s="8" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="9">
+        <v>2</v>
+      </c>
+      <c r="C5" s="10">
         <v>0.1</v>
       </c>
-      <c r="C5" s="15"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17"/>
-      <c r="H5" s="7"/>
-    </row>
-    <row r="6" ht="20" customHeight="1" spans="1:8">
-      <c r="A6" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="B6" s="14">
+      <c r="D5" s="11"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="13"/>
+      <c r="I5" s="22"/>
+    </row>
+    <row r="6" ht="20" customHeight="1" spans="1:9">
+      <c r="A6" s="8" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="9">
+        <v>2</v>
+      </c>
+      <c r="C6" s="10">
         <v>0.08</v>
       </c>
-      <c r="C6" s="15"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="17"/>
-      <c r="H6" s="7"/>
-    </row>
-    <row r="7" ht="20" customHeight="1" spans="1:8">
-      <c r="A7" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B7" s="14">
+      <c r="D6" s="11"/>
+      <c r="E6" s="12"/>
+      <c r="F6" s="13"/>
+      <c r="I6" s="22"/>
+    </row>
+    <row r="7" ht="20" customHeight="1" spans="1:9">
+      <c r="A7" s="8" t="s">
+        <v>36</v>
+      </c>
+      <c r="B7" s="9">
+        <v>2</v>
+      </c>
+      <c r="C7" s="10">
         <v>0.07</v>
       </c>
-      <c r="C7" s="15"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17"/>
-      <c r="H7" s="7"/>
-    </row>
-    <row r="8" ht="20" customHeight="1" spans="1:5">
-      <c r="A8" s="18" t="s">
-        <v>36</v>
-      </c>
-      <c r="B8" s="19">
+      <c r="D7" s="11"/>
+      <c r="E7" s="12"/>
+      <c r="F7" s="13"/>
+      <c r="I7" s="22"/>
+    </row>
+    <row r="8" ht="20" customHeight="1" spans="1:6">
+      <c r="A8" s="14" t="s">
+        <v>37</v>
+      </c>
+      <c r="B8" s="9">
+        <v>5</v>
+      </c>
+      <c r="C8" s="15">
         <v>0.02</v>
       </c>
-      <c r="C8" s="20"/>
       <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-    </row>
-    <row r="9" ht="15.75" spans="1:5">
-      <c r="A9" s="21"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="23"/>
-      <c r="B11" s="23"/>
-      <c r="C11" s="23"/>
-      <c r="D11" s="23"/>
-      <c r="E11" s="23"/>
-      <c r="F11" s="23"/>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="23"/>
-      <c r="B12" s="23"/>
-      <c r="C12" s="23"/>
-      <c r="D12" s="23"/>
-      <c r="E12" s="23"/>
-      <c r="F12" s="23"/>
-    </row>
-    <row r="13" ht="15.75" spans="1:6">
-      <c r="A13" s="23"/>
-      <c r="B13" s="23"/>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="23"/>
-      <c r="F13" s="23"/>
-    </row>
-    <row r="14" ht="15.75" spans="1:6">
-      <c r="A14" s="23"/>
-      <c r="B14" s="23"/>
-      <c r="C14" s="23"/>
-      <c r="D14" s="23"/>
-      <c r="E14" s="23"/>
-      <c r="F14" s="23"/>
-    </row>
-    <row r="15" ht="15.75" spans="1:6">
-      <c r="A15" s="23"/>
-      <c r="B15" s="23"/>
-      <c r="C15" s="23"/>
-      <c r="D15" s="23"/>
-      <c r="E15" s="23"/>
-      <c r="F15" s="23"/>
-    </row>
-    <row r="16" ht="15.75" spans="1:6">
-      <c r="A16" s="23"/>
-      <c r="B16" s="23"/>
-      <c r="C16" s="23"/>
-      <c r="D16" s="23"/>
-      <c r="E16" s="23"/>
-      <c r="F16" s="23"/>
-    </row>
-    <row r="17" ht="15.75" spans="1:6">
-      <c r="A17" s="23"/>
-      <c r="B17" s="23"/>
-      <c r="C17" s="23"/>
-      <c r="D17" s="23"/>
-      <c r="E17" s="23"/>
-      <c r="F17" s="23"/>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="23"/>
-      <c r="B18" s="23"/>
-      <c r="C18" s="23"/>
-      <c r="D18" s="23"/>
-      <c r="E18" s="23"/>
-      <c r="F18" s="23"/>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="23"/>
-      <c r="B19" s="23"/>
-      <c r="C19" s="23"/>
-      <c r="D19" s="23"/>
-      <c r="E19" s="23"/>
-      <c r="F19" s="23"/>
+      <c r="E8" s="12"/>
+      <c r="F8" s="12"/>
+    </row>
+    <row r="9" ht="15.75" spans="1:6">
+      <c r="A9" s="17"/>
+      <c r="B9" s="18"/>
+      <c r="C9" s="18"/>
+      <c r="D9" s="12"/>
+      <c r="E9" s="12"/>
+      <c r="F9" s="13"/>
+    </row>
+    <row r="11" ht="15.75" spans="1:7">
+      <c r="A11" s="19"/>
+      <c r="B11" s="19"/>
+      <c r="C11" s="19"/>
+      <c r="D11" s="19"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="19"/>
+      <c r="G11" s="19"/>
+    </row>
+    <row r="12" ht="15.75" spans="1:7">
+      <c r="A12" s="19"/>
+      <c r="B12" s="19"/>
+      <c r="C12" s="19"/>
+      <c r="D12" s="19"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="19"/>
+      <c r="G12" s="19"/>
+    </row>
+    <row r="13" ht="15.75" spans="1:7">
+      <c r="A13" s="19"/>
+      <c r="B13" s="19"/>
+      <c r="C13" s="19"/>
+      <c r="D13" s="19"/>
+      <c r="E13" s="19"/>
+      <c r="F13" s="19"/>
+      <c r="G13" s="19"/>
+    </row>
+    <row r="14" ht="15.75" spans="1:7">
+      <c r="A14" s="19"/>
+      <c r="B14" s="19"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="19"/>
+      <c r="E14" s="19"/>
+      <c r="F14" s="19"/>
+      <c r="G14" s="19"/>
+    </row>
+    <row r="15" ht="15.75" spans="1:7">
+      <c r="A15" s="19"/>
+      <c r="B15" s="19"/>
+      <c r="C15" s="19"/>
+      <c r="D15" s="19"/>
+      <c r="E15" s="19"/>
+      <c r="F15" s="19"/>
+      <c r="G15" s="19"/>
+    </row>
+    <row r="16" ht="15.75" spans="1:7">
+      <c r="A16" s="19"/>
+      <c r="B16" s="19"/>
+      <c r="C16" s="19"/>
+      <c r="D16" s="19"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="19"/>
+      <c r="G16" s="19"/>
+    </row>
+    <row r="17" ht="15.75" spans="1:7">
+      <c r="A17" s="19"/>
+      <c r="B17" s="19"/>
+      <c r="C17" s="19"/>
+      <c r="D17" s="19"/>
+      <c r="E17" s="19"/>
+      <c r="F17" s="19"/>
+      <c r="G17" s="19"/>
+    </row>
+    <row r="18" ht="15.75" spans="1:7">
+      <c r="A18" s="19"/>
+      <c r="B18" s="19"/>
+      <c r="C18" s="19"/>
+      <c r="D18" s="19"/>
+      <c r="E18" s="19"/>
+      <c r="F18" s="19"/>
+      <c r="G18" s="19"/>
+    </row>
+    <row r="19" ht="15.75" spans="1:7">
+      <c r="A19" s="19"/>
+      <c r="B19" s="19"/>
+      <c r="C19" s="19"/>
+      <c r="D19" s="19"/>
+      <c r="E19" s="19"/>
+      <c r="F19" s="19"/>
+      <c r="G19" s="19"/>
     </row>
     <row r="20" spans="1:1">
-      <c r="A20" s="24"/>
+      <c r="A20" s="20"/>
     </row>
     <row r="21" spans="1:1">
-      <c r="A21" s="25"/>
+      <c r="A21" s="21"/>
     </row>
   </sheetData>
-  <mergeCells count="2">
+  <mergeCells count="3">
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
